--- a/VAR_PROD.xlsx
+++ b/VAR_PROD.xlsx
@@ -17371,6 +17371,12 @@
           <t>Arroz tipo 1</t>
         </is>
       </c>
+      <c r="E574">
+        <v>12.77</v>
+      </c>
+      <c r="F574">
+        <v>19.18</v>
+      </c>
       <c r="G574" s="2">
         <v>46266</v>
       </c>
@@ -17396,6 +17402,12 @@
           <t>Açúcar Refinado</t>
         </is>
       </c>
+      <c r="E575">
+        <v>11.62</v>
+      </c>
+      <c r="F575">
+        <v>8.949999999999999</v>
+      </c>
       <c r="G575" s="2">
         <v>46266</v>
       </c>
@@ -17421,6 +17433,12 @@
           <t>Banana</t>
         </is>
       </c>
+      <c r="E576">
+        <v>7.188</v>
+      </c>
+      <c r="F576">
+        <v>10.11</v>
+      </c>
       <c r="G576" s="2">
         <v>46266</v>
       </c>
@@ -17446,6 +17464,12 @@
           <t>Batata</t>
         </is>
       </c>
+      <c r="E577">
+        <v>42.54</v>
+      </c>
+      <c r="F577">
+        <v>19.06</v>
+      </c>
       <c r="G577" s="2">
         <v>46266</v>
       </c>
@@ -17471,6 +17495,12 @@
           <t>Café em pó</t>
         </is>
       </c>
+      <c r="E578">
+        <v>14.06</v>
+      </c>
+      <c r="F578">
+        <v>0.18</v>
+      </c>
       <c r="G578" s="2">
         <v>46266</v>
       </c>
@@ -17496,6 +17526,12 @@
           <t>Carne</t>
         </is>
       </c>
+      <c r="E579">
+        <v>320.958</v>
+      </c>
+      <c r="F579">
+        <v>-4.61</v>
+      </c>
       <c r="G579" s="2">
         <v>46266</v>
       </c>
@@ -17521,6 +17557,12 @@
           <t>Farinha de Trigo</t>
         </is>
       </c>
+      <c r="E580">
+        <v>6.42</v>
+      </c>
+      <c r="F580">
+        <v>21.48</v>
+      </c>
       <c r="G580" s="2">
         <v>46266</v>
       </c>
@@ -17546,6 +17588,12 @@
           <t>Feijão Preto</t>
         </is>
       </c>
+      <c r="E581">
+        <v>29.43</v>
+      </c>
+      <c r="F581">
+        <v>0.67</v>
+      </c>
       <c r="G581" s="2">
         <v>46266</v>
       </c>
@@ -17571,6 +17619,12 @@
           <t>Leite</t>
         </is>
       </c>
+      <c r="E582">
+        <v>35.59999999999999</v>
+      </c>
+      <c r="F582">
+        <v>-4.49</v>
+      </c>
       <c r="G582" s="2">
         <v>46266</v>
       </c>
@@ -17596,6 +17650,12 @@
           <t>Manteiga</t>
         </is>
       </c>
+      <c r="E583">
+        <v>19.8275</v>
+      </c>
+      <c r="F583">
+        <v>8.390000000000001</v>
+      </c>
       <c r="G583" s="2">
         <v>46266</v>
       </c>
@@ -17621,6 +17681,12 @@
           <t>Pão Francês</t>
         </is>
       </c>
+      <c r="E584">
+        <v>94.95999999999999</v>
+      </c>
+      <c r="F584">
+        <v>8.550000000000001</v>
+      </c>
       <c r="G584" s="2">
         <v>46266</v>
       </c>
@@ -17646,6 +17712,12 @@
           <t>Tomate</t>
         </is>
       </c>
+      <c r="E585">
+        <v>77.61</v>
+      </c>
+      <c r="F585">
+        <v>5.96</v>
+      </c>
       <c r="G585" s="2">
         <v>46266</v>
       </c>
@@ -17671,6 +17743,12 @@
           <t>Óleo de Soja</t>
         </is>
       </c>
+      <c r="E586">
+        <v>6.222</v>
+      </c>
+      <c r="F586">
+        <v>-2.45</v>
+      </c>
       <c r="G586" s="2">
         <v>46266</v>
       </c>
@@ -36403,6 +36481,12 @@
           <t>Arroz tipo 1</t>
         </is>
       </c>
+      <c r="E1276">
+        <v>10.4925</v>
+      </c>
+      <c r="F1276">
+        <v>-6.82</v>
+      </c>
       <c r="G1276" s="2">
         <v>46266</v>
       </c>
@@ -36428,6 +36512,12 @@
           <t>Açúcar Refinado</t>
         </is>
       </c>
+      <c r="E1277">
+        <v>10.275</v>
+      </c>
+      <c r="F1277">
+        <v>-1.79</v>
+      </c>
       <c r="G1277" s="2">
         <v>46266</v>
       </c>
@@ -36453,6 +36543,12 @@
           <t>Banana</t>
         </is>
       </c>
+      <c r="E1278">
+        <v>6.435</v>
+      </c>
+      <c r="F1278">
+        <v>-9.390000000000001</v>
+      </c>
       <c r="G1278" s="2">
         <v>46266</v>
       </c>
@@ -36478,6 +36574,12 @@
           <t>Batata</t>
         </is>
       </c>
+      <c r="E1279">
+        <v>35.77500000000001</v>
+      </c>
+      <c r="F1279">
+        <v>9.66</v>
+      </c>
       <c r="G1279" s="2">
         <v>46266</v>
       </c>
@@ -36503,6 +36605,12 @@
           <t>Café em pó</t>
         </is>
       </c>
+      <c r="E1280">
+        <v>13.294</v>
+      </c>
+      <c r="F1280">
+        <v>-6.08</v>
+      </c>
       <c r="G1280" s="2">
         <v>46266</v>
       </c>
@@ -36528,6 +36636,12 @@
           <t>Carne</t>
         </is>
       </c>
+      <c r="E1281">
+        <v>327.7449999999999</v>
+      </c>
+      <c r="F1281">
+        <v>-9.31</v>
+      </c>
       <c r="G1281" s="2">
         <v>46266</v>
       </c>
@@ -36553,6 +36667,12 @@
           <t>Farinha de Trigo</t>
         </is>
       </c>
+      <c r="E1282">
+        <v>5.535</v>
+      </c>
+      <c r="F1282">
+        <v>2.86</v>
+      </c>
       <c r="G1282" s="2">
         <v>46266</v>
       </c>
@@ -36578,6 +36698,12 @@
           <t>Feijão Preto</t>
         </is>
       </c>
+      <c r="E1283">
+        <v>26.80875</v>
+      </c>
+      <c r="F1283">
+        <v>-9.91</v>
+      </c>
       <c r="G1283" s="2">
         <v>46266</v>
       </c>
@@ -36603,6 +36729,12 @@
           <t>Leite</t>
         </is>
       </c>
+      <c r="E1284">
+        <v>37.9875</v>
+      </c>
+      <c r="F1284">
+        <v>-1.2</v>
+      </c>
       <c r="G1284" s="2">
         <v>46266</v>
       </c>
@@ -36628,6 +36760,12 @@
           <t>Manteiga</t>
         </is>
       </c>
+      <c r="E1285">
+        <v>20.30125</v>
+      </c>
+      <c r="F1285">
+        <v>-8.06</v>
+      </c>
       <c r="G1285" s="2">
         <v>46266</v>
       </c>
@@ -36653,6 +36791,12 @@
           <t>Pão Francês</t>
         </is>
       </c>
+      <c r="E1286">
+        <v>93.64999999999999</v>
+      </c>
+      <c r="F1286">
+        <v>-0.63</v>
+      </c>
       <c r="G1286" s="2">
         <v>46266</v>
       </c>
@@ -36678,6 +36822,12 @@
           <t>Tomate</t>
         </is>
       </c>
+      <c r="E1287">
+        <v>102.765</v>
+      </c>
+      <c r="F1287">
+        <v>53.61</v>
+      </c>
       <c r="G1287" s="2">
         <v>46266</v>
       </c>
@@ -36703,6 +36853,12 @@
           <t>Óleo de Soja</t>
         </is>
       </c>
+      <c r="E1288">
+        <v>6.303000000000001</v>
+      </c>
+      <c r="F1288">
+        <v>-0.47</v>
+      </c>
       <c r="G1288" s="2">
         <v>46266</v>
       </c>
@@ -54538,6 +54694,12 @@
           <t>Arroz tipo 1</t>
         </is>
       </c>
+      <c r="E1978">
+        <v>9.77</v>
+      </c>
+      <c r="F1978">
+        <v>0</v>
+      </c>
       <c r="G1978" s="2">
         <v>46266</v>
       </c>
@@ -54563,6 +54725,12 @@
           <t>Açúcar Refinado</t>
         </is>
       </c>
+      <c r="E1979">
+        <v>13.33</v>
+      </c>
+      <c r="F1979">
+        <v>0</v>
+      </c>
       <c r="G1979" s="2">
         <v>46266</v>
       </c>
@@ -54588,6 +54756,12 @@
           <t>Banana</t>
         </is>
       </c>
+      <c r="E1980">
+        <v>5.988</v>
+      </c>
+      <c r="F1980">
+        <v>0</v>
+      </c>
       <c r="G1980" s="2">
         <v>46266</v>
       </c>
@@ -54613,6 +54787,12 @@
           <t>Batata</t>
         </is>
       </c>
+      <c r="E1981">
+        <v>35.76</v>
+      </c>
+      <c r="F1981">
+        <v>-5.3</v>
+      </c>
       <c r="G1981" s="2">
         <v>46266</v>
       </c>
@@ -54638,6 +54818,12 @@
           <t>Café em pó</t>
         </is>
       </c>
+      <c r="E1982">
+        <v>13.68</v>
+      </c>
+      <c r="F1982">
+        <v>-2.62</v>
+      </c>
       <c r="G1982" s="2">
         <v>46266</v>
       </c>
@@ -54663,6 +54849,12 @@
           <t>Carne</t>
         </is>
       </c>
+      <c r="E1983">
+        <v>318.604</v>
+      </c>
+      <c r="F1983">
+        <v>-1.24</v>
+      </c>
       <c r="G1983" s="2">
         <v>46266</v>
       </c>
@@ -54688,6 +54880,12 @@
           <t>Farinha de Trigo</t>
         </is>
       </c>
+      <c r="E1984">
+        <v>5.995</v>
+      </c>
+      <c r="F1984">
+        <v>0</v>
+      </c>
       <c r="G1984" s="2">
         <v>46266</v>
       </c>
@@ -54713,6 +54911,12 @@
           <t>Feijão Preto</t>
         </is>
       </c>
+      <c r="E1985">
+        <v>28.95</v>
+      </c>
+      <c r="F1985">
+        <v>0</v>
+      </c>
       <c r="G1985" s="2">
         <v>46266</v>
       </c>
@@ -54738,6 +54942,12 @@
           <t>Leite</t>
         </is>
       </c>
+      <c r="E1986">
+        <v>38.02500000000001</v>
+      </c>
+      <c r="F1986">
+        <v>-0.98</v>
+      </c>
       <c r="G1986" s="2">
         <v>46266</v>
       </c>
@@ -54763,6 +54973,12 @@
           <t>Manteiga</t>
         </is>
       </c>
+      <c r="E1987">
+        <v>23.0725</v>
+      </c>
+      <c r="F1987">
+        <v>-1.45</v>
+      </c>
       <c r="G1987" s="2">
         <v>46266</v>
       </c>
@@ -54788,6 +55004,12 @@
           <t>Pão Francês</t>
         </is>
       </c>
+      <c r="E1988">
+        <v>91.56</v>
+      </c>
+      <c r="F1988">
+        <v>0</v>
+      </c>
       <c r="G1988" s="2">
         <v>46266</v>
       </c>
@@ -54813,6 +55035,12 @@
           <t>Tomate</t>
         </is>
       </c>
+      <c r="E1989">
+        <v>49.41</v>
+      </c>
+      <c r="F1989">
+        <v>-4.69</v>
+      </c>
       <c r="G1989" s="2">
         <v>46266</v>
       </c>
@@ -54838,6 +55066,12 @@
           <t>Óleo de Soja</t>
         </is>
       </c>
+      <c r="E1990">
+        <v>7.116000000000001</v>
+      </c>
+      <c r="F1990">
+        <v>-0.63</v>
+      </c>
       <c r="G1990" s="2">
         <v>46266</v>
       </c>
@@ -57502,6 +57736,12 @@
           <t>Arroz tipo 1</t>
         </is>
       </c>
+      <c r="E2095">
+        <v>11.6</v>
+      </c>
+      <c r="F2095">
+        <v>10.79</v>
+      </c>
       <c r="G2095" s="2">
         <v>46266</v>
       </c>
@@ -57527,6 +57767,12 @@
           <t>Açúcar Refinado</t>
         </is>
       </c>
+      <c r="E2096">
+        <v>11.2</v>
+      </c>
+      <c r="F2096">
+        <v>-0.44</v>
+      </c>
       <c r="G2096" s="2">
         <v>46266</v>
       </c>
@@ -57552,6 +57798,12 @@
           <t>Banana</t>
         </is>
       </c>
+      <c r="E2097">
+        <v>7.919999999999999</v>
+      </c>
+      <c r="F2097">
+        <v>-3.04</v>
+      </c>
       <c r="G2097" s="2">
         <v>46266</v>
       </c>
@@ -57577,6 +57829,12 @@
           <t>Batata</t>
         </is>
       </c>
+      <c r="E2098">
+        <v>40.5</v>
+      </c>
+      <c r="F2098">
+        <v>4.49</v>
+      </c>
       <c r="G2098" s="2">
         <v>46266</v>
       </c>
@@ -57602,6 +57860,12 @@
           <t>Café em pó</t>
         </is>
       </c>
+      <c r="E2099">
+        <v>14.106</v>
+      </c>
+      <c r="F2099">
+        <v>1.67</v>
+      </c>
       <c r="G2099" s="2">
         <v>46266</v>
       </c>
@@ -57627,6 +57891,12 @@
           <t>Carne</t>
         </is>
       </c>
+      <c r="E2100">
+        <v>336.996</v>
+      </c>
+      <c r="F2100">
+        <v>-1.84</v>
+      </c>
       <c r="G2100" s="2">
         <v>46266</v>
       </c>
@@ -57652,6 +57922,12 @@
           <t>Farinha de Trigo</t>
         </is>
       </c>
+      <c r="E2101">
+        <v>5.51</v>
+      </c>
+      <c r="F2101">
+        <v>8.460000000000001</v>
+      </c>
       <c r="G2101" s="2">
         <v>46266</v>
       </c>
@@ -57677,6 +57953,12 @@
           <t>Feijão Preto</t>
         </is>
       </c>
+      <c r="E2102">
+        <v>28.44</v>
+      </c>
+      <c r="F2102">
+        <v>6.64</v>
+      </c>
       <c r="G2102" s="2">
         <v>46266</v>
       </c>
@@ -57702,6 +57984,12 @@
           <t>Leite</t>
         </is>
       </c>
+      <c r="E2103">
+        <v>36.4</v>
+      </c>
+      <c r="F2103">
+        <v>-1.15</v>
+      </c>
       <c r="G2103" s="2">
         <v>46266</v>
       </c>
@@ -57727,6 +58015,12 @@
           <t>Manteiga</t>
         </is>
       </c>
+      <c r="E2104">
+        <v>19.945</v>
+      </c>
+      <c r="F2104">
+        <v>-1.4</v>
+      </c>
       <c r="G2104" s="2">
         <v>46266</v>
       </c>
@@ -57752,6 +58046,12 @@
           <t>Pão Francês</t>
         </is>
       </c>
+      <c r="E2105">
+        <v>101.1</v>
+      </c>
+      <c r="F2105">
+        <v>7.42</v>
+      </c>
       <c r="G2105" s="2">
         <v>46266</v>
       </c>
@@ -57777,6 +58077,12 @@
           <t>Tomate</t>
         </is>
       </c>
+      <c r="E2106">
+        <v>118.08</v>
+      </c>
+      <c r="F2106">
+        <v>58.33</v>
+      </c>
       <c r="G2106" s="2">
         <v>46266</v>
       </c>
@@ -57801,6 +58107,12 @@
         <is>
           <t>Óleo de Soja</t>
         </is>
+      </c>
+      <c r="E2107">
+        <v>6.45</v>
+      </c>
+      <c r="F2107">
+        <v>1.85</v>
       </c>
       <c r="G2107" s="2">
         <v>46266</v>

--- a/VAR_PROD.xlsx
+++ b/VAR_PROD.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2107"/>
+  <dimension ref="A1:G2224"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="7" max="7" width="20.7109375" style="2" customWidth="1"/>
@@ -29097,6 +29097,9 @@
           <t>Arroz tipo 1</t>
         </is>
       </c>
+      <c r="E990">
+        <v>12.6</v>
+      </c>
       <c r="G990" s="2">
         <v>46235</v>
       </c>
@@ -29122,6 +29125,9 @@
           <t>Açúcar Refinado</t>
         </is>
       </c>
+      <c r="E991">
+        <v>12.06</v>
+      </c>
       <c r="G991" s="2">
         <v>46235</v>
       </c>
@@ -29147,6 +29153,9 @@
           <t>Banana</t>
         </is>
       </c>
+      <c r="E992">
+        <v>7.184</v>
+      </c>
       <c r="G992" s="2">
         <v>46235</v>
       </c>
@@ -29172,6 +29181,9 @@
           <t>Batata</t>
         </is>
       </c>
+      <c r="E993">
+        <v>31.86</v>
+      </c>
       <c r="G993" s="2">
         <v>46235</v>
       </c>
@@ -29197,6 +29209,9 @@
           <t>Café em pó</t>
         </is>
       </c>
+      <c r="E994">
+        <v>15.594</v>
+      </c>
       <c r="G994" s="2">
         <v>46235</v>
       </c>
@@ -29222,6 +29237,9 @@
           <t>Carne</t>
         </is>
       </c>
+      <c r="E995">
+        <v>260.634</v>
+      </c>
       <c r="G995" s="2">
         <v>46235</v>
       </c>
@@ -29247,6 +29265,9 @@
           <t>Farinha de Trigo</t>
         </is>
       </c>
+      <c r="E996">
+        <v>5.81</v>
+      </c>
       <c r="G996" s="2">
         <v>46235</v>
       </c>
@@ -29272,6 +29293,9 @@
           <t>Feijão Preto</t>
         </is>
       </c>
+      <c r="E997">
+        <v>28.425</v>
+      </c>
       <c r="G997" s="2">
         <v>46235</v>
       </c>
@@ -29297,6 +29321,9 @@
           <t>Leite</t>
         </is>
       </c>
+      <c r="E998">
+        <v>38.4</v>
+      </c>
       <c r="G998" s="2">
         <v>46235</v>
       </c>
@@ -29322,6 +29349,9 @@
           <t>Manteiga</t>
         </is>
       </c>
+      <c r="E999">
+        <v>20.7425</v>
+      </c>
       <c r="G999" s="2">
         <v>46235</v>
       </c>
@@ -29347,6 +29377,9 @@
           <t>Pão Francês</t>
         </is>
       </c>
+      <c r="E1000">
+        <v>81.40000000000001</v>
+      </c>
       <c r="G1000" s="2">
         <v>46235</v>
       </c>
@@ -29372,6 +29405,9 @@
           <t>Tomate</t>
         </is>
       </c>
+      <c r="E1001">
+        <v>73.28999999999999</v>
+      </c>
       <c r="G1001" s="2">
         <v>46235</v>
       </c>
@@ -29397,6 +29433,9 @@
           <t>Óleo de Soja</t>
         </is>
       </c>
+      <c r="E1002">
+        <v>6.732</v>
+      </c>
       <c r="G1002" s="2">
         <v>46235</v>
       </c>
@@ -45763,6 +45802,12 @@
           <t>Arroz tipo 1</t>
         </is>
       </c>
+      <c r="E1627">
+        <v>10.22</v>
+      </c>
+      <c r="F1627">
+        <v>6.24</v>
+      </c>
       <c r="G1627" s="2">
         <v>46266</v>
       </c>
@@ -45788,6 +45833,12 @@
           <t>Açúcar Refinado</t>
         </is>
       </c>
+      <c r="E1628">
+        <v>10.93</v>
+      </c>
+      <c r="F1628">
+        <v>-0.55</v>
+      </c>
       <c r="G1628" s="2">
         <v>46266</v>
       </c>
@@ -45813,6 +45864,12 @@
           <t>Banana</t>
         </is>
       </c>
+      <c r="E1629">
+        <v>6.588</v>
+      </c>
+      <c r="F1629">
+        <v>0</v>
+      </c>
       <c r="G1629" s="2">
         <v>46266</v>
       </c>
@@ -45838,6 +45895,12 @@
           <t>Batata</t>
         </is>
       </c>
+      <c r="E1630">
+        <v>29.88</v>
+      </c>
+      <c r="F1630">
+        <v>2.61</v>
+      </c>
       <c r="G1630" s="2">
         <v>46266</v>
       </c>
@@ -45863,6 +45926,12 @@
           <t>Café em pó</t>
         </is>
       </c>
+      <c r="E1631">
+        <v>13.586</v>
+      </c>
+      <c r="F1631">
+        <v>-2.44</v>
+      </c>
       <c r="G1631" s="2">
         <v>46266</v>
       </c>
@@ -45888,6 +45957,12 @@
           <t>Carne</t>
         </is>
       </c>
+      <c r="E1632">
+        <v>315.304</v>
+      </c>
+      <c r="F1632">
+        <v>-2.56</v>
+      </c>
       <c r="G1632" s="2">
         <v>46266</v>
       </c>
@@ -45913,6 +45988,12 @@
           <t>Farinha de Trigo</t>
         </is>
       </c>
+      <c r="E1633">
+        <v>5.375</v>
+      </c>
+      <c r="F1633">
+        <v>-0.74</v>
+      </c>
       <c r="G1633" s="2">
         <v>46266</v>
       </c>
@@ -45938,6 +46019,12 @@
           <t>Feijão Preto</t>
         </is>
       </c>
+      <c r="E1634">
+        <v>27.39</v>
+      </c>
+      <c r="F1634">
+        <v>4.1</v>
+      </c>
       <c r="G1634" s="2">
         <v>46266</v>
       </c>
@@ -45963,6 +46050,12 @@
           <t>Leite</t>
         </is>
       </c>
+      <c r="E1635">
+        <v>36.25</v>
+      </c>
+      <c r="F1635">
+        <v>-1.69</v>
+      </c>
       <c r="G1635" s="2">
         <v>46266</v>
       </c>
@@ -45988,6 +46081,12 @@
           <t>Manteiga</t>
         </is>
       </c>
+      <c r="E1636">
+        <v>19.1025</v>
+      </c>
+      <c r="F1636">
+        <v>3.17</v>
+      </c>
       <c r="G1636" s="2">
         <v>46266</v>
       </c>
@@ -46013,6 +46112,12 @@
           <t>Pão Francês</t>
         </is>
       </c>
+      <c r="E1637">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="F1637">
+        <v>2.4</v>
+      </c>
       <c r="G1637" s="2">
         <v>46266</v>
       </c>
@@ -46038,6 +46143,12 @@
           <t>Tomate</t>
         </is>
       </c>
+      <c r="E1638">
+        <v>107.82</v>
+      </c>
+      <c r="F1638">
+        <v>105.96</v>
+      </c>
       <c r="G1638" s="2">
         <v>46266</v>
       </c>
@@ -46063,6 +46174,12 @@
           <t>Óleo de Soja</t>
         </is>
       </c>
+      <c r="E1639">
+        <v>6.411</v>
+      </c>
+      <c r="F1639">
+        <v>1.14</v>
+      </c>
       <c r="G1639" s="2">
         <v>46266</v>
       </c>
@@ -58115,6 +58232,3048 @@
         <v>1.85</v>
       </c>
       <c r="G2107" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2108" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="C2108" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2108" t="inlineStr">
+        <is>
+          <t>Arroz tipo 1</t>
+        </is>
+      </c>
+      <c r="G2108" s="2">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2109" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="C2109" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2109" t="inlineStr">
+        <is>
+          <t>Açúcar Refinado</t>
+        </is>
+      </c>
+      <c r="G2109" s="2">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2110" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="C2110" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2110" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="G2110" s="2">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2111" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="C2111" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2111" t="inlineStr">
+        <is>
+          <t>Batata</t>
+        </is>
+      </c>
+      <c r="G2111" s="2">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2112" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="C2112" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2112" t="inlineStr">
+        <is>
+          <t>Café em pó</t>
+        </is>
+      </c>
+      <c r="G2112" s="2">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2113" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="C2113" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2113" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="G2113" s="2">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2114" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="C2114" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2114" t="inlineStr">
+        <is>
+          <t>Farinha de Trigo</t>
+        </is>
+      </c>
+      <c r="G2114" s="2">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2115" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="C2115" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2115" t="inlineStr">
+        <is>
+          <t>Feijão Preto</t>
+        </is>
+      </c>
+      <c r="G2115" s="2">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2116" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="C2116" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2116" t="inlineStr">
+        <is>
+          <t>Leite</t>
+        </is>
+      </c>
+      <c r="G2116" s="2">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2117" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="C2117" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2117" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="G2117" s="2">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2118" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="C2118" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2118" t="inlineStr">
+        <is>
+          <t>Pão Francês</t>
+        </is>
+      </c>
+      <c r="G2118" s="2">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2119" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="C2119" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2119" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="G2119" s="2">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2120" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="C2120" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2120" t="inlineStr">
+        <is>
+          <t>Óleo de Soja</t>
+        </is>
+      </c>
+      <c r="G2120" s="2">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2121" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="C2121" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2121" t="inlineStr">
+        <is>
+          <t>Arroz tipo 1</t>
+        </is>
+      </c>
+      <c r="G2121" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2122" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="C2122" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2122" t="inlineStr">
+        <is>
+          <t>Açúcar Refinado</t>
+        </is>
+      </c>
+      <c r="G2122" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2123" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="C2123" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2123" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="G2123" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2124" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="C2124" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2124" t="inlineStr">
+        <is>
+          <t>Batata</t>
+        </is>
+      </c>
+      <c r="G2124" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2125" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="C2125" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2125" t="inlineStr">
+        <is>
+          <t>Café em pó</t>
+        </is>
+      </c>
+      <c r="G2125" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2126" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="C2126" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2126" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="G2126" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2127" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="C2127" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2127" t="inlineStr">
+        <is>
+          <t>Farinha de Trigo</t>
+        </is>
+      </c>
+      <c r="G2127" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2128">
+      <c r="A2128" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2128" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="C2128" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2128" t="inlineStr">
+        <is>
+          <t>Feijão Preto</t>
+        </is>
+      </c>
+      <c r="G2128" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="A2129" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2129" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="C2129" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2129" t="inlineStr">
+        <is>
+          <t>Leite</t>
+        </is>
+      </c>
+      <c r="G2129" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2130">
+      <c r="A2130" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2130" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="C2130" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2130" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="G2130" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2131">
+      <c r="A2131" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2131" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="C2131" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2131" t="inlineStr">
+        <is>
+          <t>Pão Francês</t>
+        </is>
+      </c>
+      <c r="G2131" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2132">
+      <c r="A2132" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2132" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="C2132" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2132" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="G2132" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2133">
+      <c r="A2133" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2133" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="C2133" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2133" t="inlineStr">
+        <is>
+          <t>Óleo de Soja</t>
+        </is>
+      </c>
+      <c r="G2133" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="2134">
+      <c r="A2134" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2134" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="C2134" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2134" t="inlineStr">
+        <is>
+          <t>Arroz tipo 1</t>
+        </is>
+      </c>
+      <c r="G2134" s="2">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="A2135" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2135" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="C2135" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2135" t="inlineStr">
+        <is>
+          <t>Açúcar Refinado</t>
+        </is>
+      </c>
+      <c r="G2135" s="2">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="2136">
+      <c r="A2136" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2136" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="C2136" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2136" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="G2136" s="2">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="2137">
+      <c r="A2137" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2137" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="C2137" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2137" t="inlineStr">
+        <is>
+          <t>Batata</t>
+        </is>
+      </c>
+      <c r="G2137" s="2">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="A2138" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2138" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="C2138" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2138" t="inlineStr">
+        <is>
+          <t>Café em pó</t>
+        </is>
+      </c>
+      <c r="G2138" s="2">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="2139">
+      <c r="A2139" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2139" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="C2139" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2139" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="G2139" s="2">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="2140">
+      <c r="A2140" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2140" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="C2140" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2140" t="inlineStr">
+        <is>
+          <t>Farinha de Trigo</t>
+        </is>
+      </c>
+      <c r="G2140" s="2">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="2141">
+      <c r="A2141" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2141" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="C2141" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2141" t="inlineStr">
+        <is>
+          <t>Feijão Preto</t>
+        </is>
+      </c>
+      <c r="G2141" s="2">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="2142">
+      <c r="A2142" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2142" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="C2142" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2142" t="inlineStr">
+        <is>
+          <t>Leite</t>
+        </is>
+      </c>
+      <c r="G2142" s="2">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="2143">
+      <c r="A2143" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2143" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="C2143" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2143" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="G2143" s="2">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="2144">
+      <c r="A2144" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2144" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="C2144" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2144" t="inlineStr">
+        <is>
+          <t>Pão Francês</t>
+        </is>
+      </c>
+      <c r="G2144" s="2">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="2145">
+      <c r="A2145" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2145" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="C2145" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2145" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="G2145" s="2">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="2146">
+      <c r="A2146" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2146" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="C2146" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2146" t="inlineStr">
+        <is>
+          <t>Óleo de Soja</t>
+        </is>
+      </c>
+      <c r="G2146" s="2">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="2147">
+      <c r="A2147" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2147" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="C2147" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2147" t="inlineStr">
+        <is>
+          <t>Arroz tipo 1</t>
+        </is>
+      </c>
+      <c r="G2147" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2148">
+      <c r="A2148" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2148" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="C2148" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2148" t="inlineStr">
+        <is>
+          <t>Açúcar Refinado</t>
+        </is>
+      </c>
+      <c r="G2148" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2149">
+      <c r="A2149" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2149" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="C2149" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2149" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="G2149" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2150">
+      <c r="A2150" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2150" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="C2150" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2150" t="inlineStr">
+        <is>
+          <t>Batata</t>
+        </is>
+      </c>
+      <c r="G2150" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2151">
+      <c r="A2151" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2151" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="C2151" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2151" t="inlineStr">
+        <is>
+          <t>Café em pó</t>
+        </is>
+      </c>
+      <c r="G2151" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2152">
+      <c r="A2152" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2152" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="C2152" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2152" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="G2152" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2153">
+      <c r="A2153" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2153" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="C2153" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2153" t="inlineStr">
+        <is>
+          <t>Farinha de Trigo</t>
+        </is>
+      </c>
+      <c r="G2153" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2154">
+      <c r="A2154" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2154" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="C2154" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2154" t="inlineStr">
+        <is>
+          <t>Feijão Preto</t>
+        </is>
+      </c>
+      <c r="G2154" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2155">
+      <c r="A2155" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2155" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="C2155" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2155" t="inlineStr">
+        <is>
+          <t>Leite</t>
+        </is>
+      </c>
+      <c r="G2155" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2156">
+      <c r="A2156" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2156" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="C2156" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2156" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="G2156" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2157">
+      <c r="A2157" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2157" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="C2157" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2157" t="inlineStr">
+        <is>
+          <t>Pão Francês</t>
+        </is>
+      </c>
+      <c r="G2157" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2158">
+      <c r="A2158" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2158" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="C2158" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2158" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="G2158" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2159">
+      <c r="A2159" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2159" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="C2159" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2159" t="inlineStr">
+        <is>
+          <t>Óleo de Soja</t>
+        </is>
+      </c>
+      <c r="G2159" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="2160">
+      <c r="A2160" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2160" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="C2160" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2160" t="inlineStr">
+        <is>
+          <t>Arroz tipo 1</t>
+        </is>
+      </c>
+      <c r="G2160" s="2">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="2161">
+      <c r="A2161" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2161" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="C2161" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2161" t="inlineStr">
+        <is>
+          <t>Açúcar Refinado</t>
+        </is>
+      </c>
+      <c r="G2161" s="2">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="2162">
+      <c r="A2162" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2162" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="C2162" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2162" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="G2162" s="2">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="2163">
+      <c r="A2163" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2163" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="C2163" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2163" t="inlineStr">
+        <is>
+          <t>Batata</t>
+        </is>
+      </c>
+      <c r="G2163" s="2">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="2164">
+      <c r="A2164" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2164" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="C2164" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2164" t="inlineStr">
+        <is>
+          <t>Café em pó</t>
+        </is>
+      </c>
+      <c r="G2164" s="2">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="2165">
+      <c r="A2165" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2165" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="C2165" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2165" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="G2165" s="2">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="2166">
+      <c r="A2166" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2166" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="C2166" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2166" t="inlineStr">
+        <is>
+          <t>Farinha de Trigo</t>
+        </is>
+      </c>
+      <c r="G2166" s="2">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="2167">
+      <c r="A2167" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2167" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="C2167" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2167" t="inlineStr">
+        <is>
+          <t>Feijão Preto</t>
+        </is>
+      </c>
+      <c r="G2167" s="2">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="2168">
+      <c r="A2168" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2168" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="C2168" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2168" t="inlineStr">
+        <is>
+          <t>Leite</t>
+        </is>
+      </c>
+      <c r="G2168" s="2">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="2169">
+      <c r="A2169" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2169" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="C2169" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2169" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="G2169" s="2">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="2170">
+      <c r="A2170" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2170" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="C2170" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2170" t="inlineStr">
+        <is>
+          <t>Pão Francês</t>
+        </is>
+      </c>
+      <c r="G2170" s="2">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="2171">
+      <c r="A2171" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2171" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="C2171" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2171" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="G2171" s="2">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="2172">
+      <c r="A2172" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2172" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="C2172" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2172" t="inlineStr">
+        <is>
+          <t>Óleo de Soja</t>
+        </is>
+      </c>
+      <c r="G2172" s="2">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="2173">
+      <c r="A2173" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2173" t="inlineStr">
+        <is>
+          <t>Junho</t>
+        </is>
+      </c>
+      <c r="C2173" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2173" t="inlineStr">
+        <is>
+          <t>Arroz tipo 1</t>
+        </is>
+      </c>
+      <c r="G2173" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2174">
+      <c r="A2174" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2174" t="inlineStr">
+        <is>
+          <t>Junho</t>
+        </is>
+      </c>
+      <c r="C2174" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2174" t="inlineStr">
+        <is>
+          <t>Açúcar Refinado</t>
+        </is>
+      </c>
+      <c r="G2174" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2175">
+      <c r="A2175" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2175" t="inlineStr">
+        <is>
+          <t>Junho</t>
+        </is>
+      </c>
+      <c r="C2175" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2175" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="G2175" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2176">
+      <c r="A2176" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2176" t="inlineStr">
+        <is>
+          <t>Junho</t>
+        </is>
+      </c>
+      <c r="C2176" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2176" t="inlineStr">
+        <is>
+          <t>Batata</t>
+        </is>
+      </c>
+      <c r="G2176" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2177">
+      <c r="A2177" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2177" t="inlineStr">
+        <is>
+          <t>Junho</t>
+        </is>
+      </c>
+      <c r="C2177" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2177" t="inlineStr">
+        <is>
+          <t>Café em pó</t>
+        </is>
+      </c>
+      <c r="G2177" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2178">
+      <c r="A2178" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2178" t="inlineStr">
+        <is>
+          <t>Junho</t>
+        </is>
+      </c>
+      <c r="C2178" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2178" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="G2178" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2179">
+      <c r="A2179" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2179" t="inlineStr">
+        <is>
+          <t>Junho</t>
+        </is>
+      </c>
+      <c r="C2179" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2179" t="inlineStr">
+        <is>
+          <t>Farinha de Trigo</t>
+        </is>
+      </c>
+      <c r="G2179" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2180">
+      <c r="A2180" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2180" t="inlineStr">
+        <is>
+          <t>Junho</t>
+        </is>
+      </c>
+      <c r="C2180" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2180" t="inlineStr">
+        <is>
+          <t>Feijão Preto</t>
+        </is>
+      </c>
+      <c r="G2180" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2181">
+      <c r="A2181" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2181" t="inlineStr">
+        <is>
+          <t>Junho</t>
+        </is>
+      </c>
+      <c r="C2181" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2181" t="inlineStr">
+        <is>
+          <t>Leite</t>
+        </is>
+      </c>
+      <c r="G2181" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2182">
+      <c r="A2182" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2182" t="inlineStr">
+        <is>
+          <t>Junho</t>
+        </is>
+      </c>
+      <c r="C2182" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2182" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="G2182" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2183">
+      <c r="A2183" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2183" t="inlineStr">
+        <is>
+          <t>Junho</t>
+        </is>
+      </c>
+      <c r="C2183" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2183" t="inlineStr">
+        <is>
+          <t>Pão Francês</t>
+        </is>
+      </c>
+      <c r="G2183" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2184">
+      <c r="A2184" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2184" t="inlineStr">
+        <is>
+          <t>Junho</t>
+        </is>
+      </c>
+      <c r="C2184" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2184" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="G2184" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2185">
+      <c r="A2185" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2185" t="inlineStr">
+        <is>
+          <t>Junho</t>
+        </is>
+      </c>
+      <c r="C2185" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2185" t="inlineStr">
+        <is>
+          <t>Óleo de Soja</t>
+        </is>
+      </c>
+      <c r="G2185" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="2186">
+      <c r="A2186" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2186" t="inlineStr">
+        <is>
+          <t>Julho</t>
+        </is>
+      </c>
+      <c r="C2186" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2186" t="inlineStr">
+        <is>
+          <t>Arroz tipo 1</t>
+        </is>
+      </c>
+      <c r="G2186" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2187">
+      <c r="A2187" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2187" t="inlineStr">
+        <is>
+          <t>Julho</t>
+        </is>
+      </c>
+      <c r="C2187" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2187" t="inlineStr">
+        <is>
+          <t>Açúcar Refinado</t>
+        </is>
+      </c>
+      <c r="G2187" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2188">
+      <c r="A2188" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2188" t="inlineStr">
+        <is>
+          <t>Julho</t>
+        </is>
+      </c>
+      <c r="C2188" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2188" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="G2188" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2189">
+      <c r="A2189" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2189" t="inlineStr">
+        <is>
+          <t>Julho</t>
+        </is>
+      </c>
+      <c r="C2189" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2189" t="inlineStr">
+        <is>
+          <t>Batata</t>
+        </is>
+      </c>
+      <c r="G2189" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2190">
+      <c r="A2190" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2190" t="inlineStr">
+        <is>
+          <t>Julho</t>
+        </is>
+      </c>
+      <c r="C2190" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2190" t="inlineStr">
+        <is>
+          <t>Café em pó</t>
+        </is>
+      </c>
+      <c r="G2190" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2191">
+      <c r="A2191" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2191" t="inlineStr">
+        <is>
+          <t>Julho</t>
+        </is>
+      </c>
+      <c r="C2191" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2191" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="G2191" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2192">
+      <c r="A2192" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2192" t="inlineStr">
+        <is>
+          <t>Julho</t>
+        </is>
+      </c>
+      <c r="C2192" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2192" t="inlineStr">
+        <is>
+          <t>Farinha de Trigo</t>
+        </is>
+      </c>
+      <c r="G2192" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2193">
+      <c r="A2193" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2193" t="inlineStr">
+        <is>
+          <t>Julho</t>
+        </is>
+      </c>
+      <c r="C2193" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2193" t="inlineStr">
+        <is>
+          <t>Feijão Preto</t>
+        </is>
+      </c>
+      <c r="G2193" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2194">
+      <c r="A2194" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2194" t="inlineStr">
+        <is>
+          <t>Julho</t>
+        </is>
+      </c>
+      <c r="C2194" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2194" t="inlineStr">
+        <is>
+          <t>Leite</t>
+        </is>
+      </c>
+      <c r="G2194" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2195">
+      <c r="A2195" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2195" t="inlineStr">
+        <is>
+          <t>Julho</t>
+        </is>
+      </c>
+      <c r="C2195" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2195" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="G2195" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2196">
+      <c r="A2196" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2196" t="inlineStr">
+        <is>
+          <t>Julho</t>
+        </is>
+      </c>
+      <c r="C2196" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2196" t="inlineStr">
+        <is>
+          <t>Pão Francês</t>
+        </is>
+      </c>
+      <c r="G2196" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2197">
+      <c r="A2197" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2197" t="inlineStr">
+        <is>
+          <t>Julho</t>
+        </is>
+      </c>
+      <c r="C2197" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2197" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="G2197" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2198">
+      <c r="A2198" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2198" t="inlineStr">
+        <is>
+          <t>Julho</t>
+        </is>
+      </c>
+      <c r="C2198" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2198" t="inlineStr">
+        <is>
+          <t>Óleo de Soja</t>
+        </is>
+      </c>
+      <c r="G2198" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="2199">
+      <c r="A2199" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2199" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C2199" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2199" t="inlineStr">
+        <is>
+          <t>Arroz tipo 1</t>
+        </is>
+      </c>
+      <c r="E2199">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="G2199" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="2200">
+      <c r="A2200" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2200" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C2200" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2200" t="inlineStr">
+        <is>
+          <t>Açúcar Refinado</t>
+        </is>
+      </c>
+      <c r="E2200">
+        <v>11.29</v>
+      </c>
+      <c r="G2200" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="2201">
+      <c r="A2201" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2201" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C2201" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2201" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="E2201">
+        <v>6.752</v>
+      </c>
+      <c r="G2201" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="2202">
+      <c r="A2202" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2202" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C2202" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2202" t="inlineStr">
+        <is>
+          <t>Batata</t>
+        </is>
+      </c>
+      <c r="E2202">
+        <v>32.94</v>
+      </c>
+      <c r="G2202" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="2203">
+      <c r="A2203" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2203" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C2203" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2203" t="inlineStr">
+        <is>
+          <t>Café em pó</t>
+        </is>
+      </c>
+      <c r="E2203">
+        <v>14.144</v>
+      </c>
+      <c r="G2203" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="2204">
+      <c r="A2204" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2204" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C2204" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2204" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="E2204">
+        <v>351.692</v>
+      </c>
+      <c r="G2204" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="2205">
+      <c r="A2205" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2205" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C2205" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2205" t="inlineStr">
+        <is>
+          <t>Farinha de Trigo</t>
+        </is>
+      </c>
+      <c r="E2205">
+        <v>6.149999999999999</v>
+      </c>
+      <c r="G2205" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="2206">
+      <c r="A2206" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2206" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C2206" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2206" t="inlineStr">
+        <is>
+          <t>Feijão Preto</t>
+        </is>
+      </c>
+      <c r="E2206">
+        <v>29.43</v>
+      </c>
+      <c r="G2206" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="2207">
+      <c r="A2207" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2207" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C2207" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2207" t="inlineStr">
+        <is>
+          <t>Leite</t>
+        </is>
+      </c>
+      <c r="E2207">
+        <v>43.325</v>
+      </c>
+      <c r="G2207" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="2208">
+      <c r="A2208" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2208" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C2208" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2208" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="E2208">
+        <v>21.0125</v>
+      </c>
+      <c r="G2208" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="2209">
+      <c r="A2209" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2209" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C2209" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2209" t="inlineStr">
+        <is>
+          <t>Pão Francês</t>
+        </is>
+      </c>
+      <c r="E2209">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="G2209" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="2210">
+      <c r="A2210" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2210" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C2210" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2210" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="E2210">
+        <v>82.08000000000001</v>
+      </c>
+      <c r="G2210" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="2211">
+      <c r="A2211" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2211" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C2211" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2211" t="inlineStr">
+        <is>
+          <t>Óleo de Soja</t>
+        </is>
+      </c>
+      <c r="E2211">
+        <v>7.74</v>
+      </c>
+      <c r="G2211" s="2">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="2212">
+      <c r="A2212" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2212" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="C2212" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2212" t="inlineStr">
+        <is>
+          <t>Arroz tipo 1</t>
+        </is>
+      </c>
+      <c r="E2212">
+        <v>10.79</v>
+      </c>
+      <c r="F2212">
+        <v>16.15</v>
+      </c>
+      <c r="G2212" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="2213">
+      <c r="A2213" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2213" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="C2213" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2213" t="inlineStr">
+        <is>
+          <t>Açúcar Refinado</t>
+        </is>
+      </c>
+      <c r="E2213">
+        <v>11.08</v>
+      </c>
+      <c r="F2213">
+        <v>-1.86</v>
+      </c>
+      <c r="G2213" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="2214">
+      <c r="A2214" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2214" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="C2214" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2214" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="E2214">
+        <v>6.752</v>
+      </c>
+      <c r="F2214">
+        <v>0</v>
+      </c>
+      <c r="G2214" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="2215">
+      <c r="A2215" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2215" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="C2215" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2215" t="inlineStr">
+        <is>
+          <t>Batata</t>
+        </is>
+      </c>
+      <c r="E2215">
+        <v>47.56</v>
+      </c>
+      <c r="F2215">
+        <v>44.38</v>
+      </c>
+      <c r="G2215" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="2216">
+      <c r="A2216" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2216" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="C2216" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2216" t="inlineStr">
+        <is>
+          <t>Café em pó</t>
+        </is>
+      </c>
+      <c r="E2216">
+        <v>15.608</v>
+      </c>
+      <c r="F2216">
+        <v>10.35</v>
+      </c>
+      <c r="G2216" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="2217">
+      <c r="A2217" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2217" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="C2217" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2217" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="E2217">
+        <v>348.084</v>
+      </c>
+      <c r="F2217">
+        <v>-1.03</v>
+      </c>
+      <c r="G2217" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="2218">
+      <c r="A2218" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2218" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="C2218" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2218" t="inlineStr">
+        <is>
+          <t>Farinha de Trigo</t>
+        </is>
+      </c>
+      <c r="E2218">
+        <v>5.82</v>
+      </c>
+      <c r="F2218">
+        <v>-5.37</v>
+      </c>
+      <c r="G2218" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="2219">
+      <c r="A2219" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2219" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="C2219" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2219" t="inlineStr">
+        <is>
+          <t>Feijão Preto</t>
+        </is>
+      </c>
+      <c r="E2219">
+        <v>32.145</v>
+      </c>
+      <c r="F2219">
+        <v>9.23</v>
+      </c>
+      <c r="G2219" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="2220">
+      <c r="A2220" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2220" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="C2220" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2220" t="inlineStr">
+        <is>
+          <t>Leite</t>
+        </is>
+      </c>
+      <c r="E2220">
+        <v>43.7</v>
+      </c>
+      <c r="F2220">
+        <v>0.87</v>
+      </c>
+      <c r="G2220" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="2221">
+      <c r="A2221" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2221" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="C2221" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2221" t="inlineStr">
+        <is>
+          <t>Manteiga</t>
+        </is>
+      </c>
+      <c r="E2221">
+        <v>21.86</v>
+      </c>
+      <c r="F2221">
+        <v>4.03</v>
+      </c>
+      <c r="G2221" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="2222">
+      <c r="A2222" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2222" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="C2222" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2222" t="inlineStr">
+        <is>
+          <t>Pão Francês</t>
+        </is>
+      </c>
+      <c r="E2222">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="F2222">
+        <v>0</v>
+      </c>
+      <c r="G2222" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="2223">
+      <c r="A2223" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2223" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="C2223" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2223" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="E2223">
+        <v>110.88</v>
+      </c>
+      <c r="F2223">
+        <v>35.09</v>
+      </c>
+      <c r="G2223" s="2">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="2224">
+      <c r="A2224" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B2224" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="C2224" t="inlineStr">
+        <is>
+          <t>Pomerode</t>
+        </is>
+      </c>
+      <c r="D2224" t="inlineStr">
+        <is>
+          <t>Óleo de Soja</t>
+        </is>
+      </c>
+      <c r="E2224">
+        <v>8.019</v>
+      </c>
+      <c r="F2224">
+        <v>3.6</v>
+      </c>
+      <c r="G2224" s="2">
         <v>46266</v>
       </c>
     </row>

--- a/VAR_PROD.xlsx
+++ b/VAR_PROD.xlsx
@@ -40174,10 +40174,10 @@
         </is>
       </c>
       <c r="E1419">
-        <v>10.32</v>
+        <v>10.87</v>
       </c>
       <c r="F1419">
-        <v>-7.44</v>
+        <v>-2.51</v>
       </c>
       <c r="G1419" s="2">
         <v>46235</v>
@@ -40205,10 +40205,10 @@
         </is>
       </c>
       <c r="E1420">
-        <v>12.63</v>
+        <v>10.86</v>
       </c>
       <c r="F1420">
-        <v>12.17</v>
+        <v>-3.55</v>
       </c>
       <c r="G1420" s="2">
         <v>46235</v>
@@ -40236,10 +40236,10 @@
         </is>
       </c>
       <c r="E1421">
-        <v>6.288</v>
+        <v>6.188000000000001</v>
       </c>
       <c r="F1421">
-        <v>-15.26</v>
+        <v>-16.6</v>
       </c>
       <c r="G1421" s="2">
         <v>46235</v>
@@ -40267,10 +40267,10 @@
         </is>
       </c>
       <c r="E1422">
-        <v>28.74</v>
+        <v>29.14</v>
       </c>
       <c r="F1422">
-        <v>12.44</v>
+        <v>14.01</v>
       </c>
       <c r="G1422" s="2">
         <v>46235</v>
@@ -40298,10 +40298,10 @@
         </is>
       </c>
       <c r="E1423">
-        <v>16.344</v>
+        <v>15.094</v>
       </c>
       <c r="F1423">
-        <v>-4.79</v>
+        <v>-12.07</v>
       </c>
       <c r="G1423" s="2">
         <v>46235</v>
@@ -40329,10 +40329,10 @@
         </is>
       </c>
       <c r="E1424">
-        <v>316.338</v>
+        <v>338.2719999999999</v>
       </c>
       <c r="F1424">
-        <v>-9.210000000000001</v>
+        <v>-2.92</v>
       </c>
       <c r="G1424" s="2">
         <v>46235</v>
@@ -40360,10 +40360,10 @@
         </is>
       </c>
       <c r="E1425">
-        <v>5.385</v>
+        <v>5.42</v>
       </c>
       <c r="F1425">
-        <v>5.38</v>
+        <v>6.07</v>
       </c>
       <c r="G1425" s="2">
         <v>46235</v>
@@ -40391,10 +40391,10 @@
         </is>
       </c>
       <c r="E1426">
-        <v>22.005</v>
+        <v>22.905</v>
       </c>
       <c r="F1426">
-        <v>-4.55</v>
+        <v>-0.65</v>
       </c>
       <c r="G1426" s="2">
         <v>46235</v>
@@ -40422,10 +40422,10 @@
         </is>
       </c>
       <c r="E1427">
-        <v>35.625</v>
+        <v>33.95</v>
       </c>
       <c r="F1427">
-        <v>25</v>
+        <v>19.12</v>
       </c>
       <c r="G1427" s="2">
         <v>46235</v>
@@ -40453,10 +40453,10 @@
         </is>
       </c>
       <c r="E1428">
-        <v>15.405</v>
+        <v>18.3675</v>
       </c>
       <c r="F1428">
-        <v>-22.99</v>
+        <v>-8.19</v>
       </c>
       <c r="G1428" s="2">
         <v>46235</v>
@@ -40484,10 +40484,10 @@
         </is>
       </c>
       <c r="E1429">
-        <v>80.40000000000001</v>
+        <v>79.38</v>
       </c>
       <c r="F1429">
-        <v>0.35</v>
+        <v>-0.92</v>
       </c>
       <c r="G1429" s="2">
         <v>46235</v>
@@ -40515,10 +40515,10 @@
         </is>
       </c>
       <c r="E1430">
-        <v>53.865</v>
+        <v>62.91</v>
       </c>
       <c r="F1430">
-        <v>-53.89</v>
+        <v>-46.15</v>
       </c>
       <c r="G1430" s="2">
         <v>46235</v>
@@ -40546,10 +40546,10 @@
         </is>
       </c>
       <c r="E1431">
-        <v>6.9525</v>
+        <v>6.627</v>
       </c>
       <c r="F1431">
-        <v>-16.03</v>
+        <v>-19.96</v>
       </c>
       <c r="G1431" s="2">
         <v>46235</v>
@@ -42526,6 +42526,9 @@
           <t>Arroz tipo 1</t>
         </is>
       </c>
+      <c r="E1510">
+        <v>9.779999999999999</v>
+      </c>
       <c r="G1510" s="2">
         <v>46266</v>
       </c>
@@ -42551,6 +42554,9 @@
           <t>Açúcar Refinado</t>
         </is>
       </c>
+      <c r="E1511">
+        <v>10.47</v>
+      </c>
       <c r="G1511" s="2">
         <v>46266</v>
       </c>
@@ -42576,6 +42582,9 @@
           <t>Banana</t>
         </is>
       </c>
+      <c r="E1512">
+        <v>5.988</v>
+      </c>
       <c r="G1512" s="2">
         <v>46266</v>
       </c>
@@ -42601,6 +42610,9 @@
           <t>Batata</t>
         </is>
       </c>
+      <c r="E1513">
+        <v>47.94</v>
+      </c>
       <c r="G1513" s="2">
         <v>46266</v>
       </c>
@@ -42626,6 +42638,9 @@
           <t>Café em pó</t>
         </is>
       </c>
+      <c r="E1514">
+        <v>13.194</v>
+      </c>
       <c r="G1514" s="2">
         <v>46266</v>
       </c>
@@ -42651,6 +42666,9 @@
           <t>Carne</t>
         </is>
       </c>
+      <c r="E1515">
+        <v>305.1179999999999</v>
+      </c>
       <c r="G1515" s="2">
         <v>46266</v>
       </c>
@@ -42676,6 +42694,9 @@
           <t>Farinha de Trigo</t>
         </is>
       </c>
+      <c r="E1516">
+        <v>5.985</v>
+      </c>
       <c r="G1516" s="2">
         <v>46266</v>
       </c>
@@ -42701,6 +42722,9 @@
           <t>Feijão Preto</t>
         </is>
       </c>
+      <c r="E1517">
+        <v>20.52</v>
+      </c>
       <c r="G1517" s="2">
         <v>46266</v>
       </c>
@@ -42726,6 +42750,9 @@
           <t>Leite</t>
         </is>
       </c>
+      <c r="E1518">
+        <v>34.95</v>
+      </c>
       <c r="G1518" s="2">
         <v>46266</v>
       </c>
@@ -42751,6 +42778,9 @@
           <t>Manteiga</t>
         </is>
       </c>
+      <c r="E1519">
+        <v>17.955</v>
+      </c>
       <c r="G1519" s="2">
         <v>46266</v>
       </c>
@@ -42776,6 +42806,9 @@
           <t>Pão Francês</t>
         </is>
       </c>
+      <c r="E1520">
+        <v>95.40000000000001</v>
+      </c>
       <c r="G1520" s="2">
         <v>46266</v>
       </c>
@@ -42801,6 +42834,9 @@
           <t>Tomate</t>
         </is>
       </c>
+      <c r="E1521">
+        <v>116.91</v>
+      </c>
       <c r="G1521" s="2">
         <v>46266</v>
       </c>
@@ -42825,6 +42861,9 @@
         <is>
           <t>Óleo de Soja</t>
         </is>
+      </c>
+      <c r="E1522">
+        <v>6.354</v>
       </c>
       <c r="G1522" s="2">
         <v>46266</v>

--- a/VAR_PROD.xlsx
+++ b/VAR_PROD.xlsx
@@ -29305,6 +29305,12 @@
           <t>Arroz tipo 1</t>
         </is>
       </c>
+      <c r="E1003">
+        <v>12.49</v>
+      </c>
+      <c r="F1003">
+        <v>40.65</v>
+      </c>
       <c r="G1003" s="2">
         <v>46266</v>
       </c>
@@ -29330,6 +29336,12 @@
           <t>Açúcar Refinado</t>
         </is>
       </c>
+      <c r="E1004">
+        <v>11.37</v>
+      </c>
+      <c r="F1004">
+        <v>-11.03</v>
+      </c>
       <c r="G1004" s="2">
         <v>46266</v>
       </c>
@@ -29355,6 +29367,12 @@
           <t>Banana</t>
         </is>
       </c>
+      <c r="E1005">
+        <v>7.744</v>
+      </c>
+      <c r="F1005">
+        <v>-38.48</v>
+      </c>
       <c r="G1005" s="2">
         <v>46266</v>
       </c>
@@ -29380,6 +29398,12 @@
           <t>Batata</t>
         </is>
       </c>
+      <c r="E1006">
+        <v>41.94</v>
+      </c>
+      <c r="F1006">
+        <v>16.69</v>
+      </c>
       <c r="G1006" s="2">
         <v>46266</v>
       </c>
@@ -29405,6 +29429,12 @@
           <t>Café em pó</t>
         </is>
       </c>
+      <c r="E1007">
+        <v>15.528</v>
+      </c>
+      <c r="F1007">
+        <v>1.53</v>
+      </c>
       <c r="G1007" s="2">
         <v>46266</v>
       </c>
@@ -29430,6 +29460,12 @@
           <t>Carne</t>
         </is>
       </c>
+      <c r="E1008">
+        <v>237.534</v>
+      </c>
+      <c r="F1008">
+        <v>1.38</v>
+      </c>
       <c r="G1008" s="2">
         <v>46266</v>
       </c>
@@ -29455,6 +29491,12 @@
           <t>Farinha de Trigo</t>
         </is>
       </c>
+      <c r="E1009">
+        <v>5.859999999999999</v>
+      </c>
+      <c r="F1009">
+        <v>-2.09</v>
+      </c>
       <c r="G1009" s="2">
         <v>46266</v>
       </c>
@@ -29480,6 +29522,12 @@
           <t>Feijão Preto</t>
         </is>
       </c>
+      <c r="E1010">
+        <v>29.22</v>
+      </c>
+      <c r="F1010">
+        <v>53.87</v>
+      </c>
       <c r="G1010" s="2">
         <v>46266</v>
       </c>
@@ -29505,6 +29553,12 @@
           <t>Leite</t>
         </is>
       </c>
+      <c r="E1011">
+        <v>38.4</v>
+      </c>
+      <c r="F1011">
+        <v>4.07</v>
+      </c>
       <c r="G1011" s="2">
         <v>46266</v>
       </c>
@@ -29530,6 +29584,12 @@
           <t>Manteiga</t>
         </is>
       </c>
+      <c r="E1012">
+        <v>21.8675</v>
+      </c>
+      <c r="F1012">
+        <v>2.34</v>
+      </c>
       <c r="G1012" s="2">
         <v>46266</v>
       </c>
@@ -29555,6 +29615,12 @@
           <t>Pão Francês</t>
         </is>
       </c>
+      <c r="E1013">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="F1013">
+        <v>-4.47</v>
+      </c>
       <c r="G1013" s="2">
         <v>46266</v>
       </c>
@@ -29580,6 +29646,12 @@
           <t>Tomate</t>
         </is>
       </c>
+      <c r="E1014">
+        <v>110.79</v>
+      </c>
+      <c r="F1014">
+        <v>29.72</v>
+      </c>
       <c r="G1014" s="2">
         <v>46266</v>
       </c>
@@ -29604,6 +29676,12 @@
         <is>
           <t>Óleo de Soja</t>
         </is>
+      </c>
+      <c r="E1015">
+        <v>6.792000000000001</v>
+      </c>
+      <c r="F1015">
+        <v>9.529999999999999</v>
       </c>
       <c r="G1015" s="2">
         <v>46266</v>

--- a/VAR_PROD.xlsx
+++ b/VAR_PROD.xlsx
@@ -17332,6 +17332,12 @@
           <t>Arroz tipo 1</t>
         </is>
       </c>
+      <c r="E574">
+        <v>12.64</v>
+      </c>
+      <c r="F574">
+        <v>67.2</v>
+      </c>
       <c r="G574" s="2">
         <v>46296</v>
       </c>
@@ -17357,6 +17363,12 @@
           <t>Açúcar Refinado</t>
         </is>
       </c>
+      <c r="E575">
+        <v>10.71</v>
+      </c>
+      <c r="F575">
+        <v>8.51</v>
+      </c>
       <c r="G575" s="2">
         <v>46296</v>
       </c>
@@ -17382,6 +17394,12 @@
           <t>Banana</t>
         </is>
       </c>
+      <c r="E576">
+        <v>6.16</v>
+      </c>
+      <c r="F576">
+        <v>-14.3</v>
+      </c>
       <c r="G576" s="2">
         <v>46296</v>
       </c>
@@ -17407,6 +17425,12 @@
           <t>Batata</t>
         </is>
       </c>
+      <c r="E577">
+        <v>42.78</v>
+      </c>
+      <c r="F577">
+        <v>78.7</v>
+      </c>
       <c r="G577" s="2">
         <v>46296</v>
       </c>
@@ -17432,6 +17456,12 @@
           <t>Café em pó</t>
         </is>
       </c>
+      <c r="E578">
+        <v>16.226</v>
+      </c>
+      <c r="F578">
+        <v>16.27</v>
+      </c>
       <c r="G578" s="2">
         <v>46296</v>
       </c>
@@ -17457,6 +17487,12 @@
           <t>Carne</t>
         </is>
       </c>
+      <c r="E579">
+        <v>305.1179999999999</v>
+      </c>
+      <c r="F579">
+        <v>-1.34</v>
+      </c>
       <c r="G579" s="2">
         <v>46296</v>
       </c>
@@ -17482,6 +17518,12 @@
           <t>Farinha de Trigo</t>
         </is>
       </c>
+      <c r="E580">
+        <v>5.24</v>
+      </c>
+      <c r="F580">
+        <v>31.33</v>
+      </c>
       <c r="G580" s="2">
         <v>46296</v>
       </c>
@@ -17507,6 +17549,12 @@
           <t>Feijão Preto</t>
         </is>
       </c>
+      <c r="E581">
+        <v>26.25</v>
+      </c>
+      <c r="F581">
+        <v>27.09</v>
+      </c>
       <c r="G581" s="2">
         <v>46296</v>
       </c>
@@ -17532,6 +17580,12 @@
           <t>Leite</t>
         </is>
       </c>
+      <c r="E582">
+        <v>38.85</v>
+      </c>
+      <c r="F582">
+        <v>26.03</v>
+      </c>
       <c r="G582" s="2">
         <v>46296</v>
       </c>
@@ -17557,6 +17611,12 @@
           <t>Manteiga</t>
         </is>
       </c>
+      <c r="E583">
+        <v>20.6175</v>
+      </c>
+      <c r="F583">
+        <v>8.06</v>
+      </c>
       <c r="G583" s="2">
         <v>46296</v>
       </c>
@@ -17582,6 +17642,12 @@
           <t>Pão Francês</t>
         </is>
       </c>
+      <c r="E584">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="F584">
+        <v>19.47</v>
+      </c>
       <c r="G584" s="2">
         <v>46296</v>
       </c>
@@ -17607,6 +17673,12 @@
           <t>Tomate</t>
         </is>
       </c>
+      <c r="E585">
+        <v>139.23</v>
+      </c>
+      <c r="F585">
+        <v>54.85</v>
+      </c>
       <c r="G585" s="2">
         <v>46296</v>
       </c>
@@ -17632,6 +17704,12 @@
           <t>Óleo de Soja</t>
         </is>
       </c>
+      <c r="E586">
+        <v>6.777</v>
+      </c>
+      <c r="F586">
+        <v>4.01</v>
+      </c>
       <c r="G586" s="2">
         <v>46296</v>
       </c>
@@ -17660,6 +17738,9 @@
       <c r="E587">
         <v>12.77</v>
       </c>
+      <c r="F587">
+        <v>1.03</v>
+      </c>
       <c r="G587" s="2">
         <v>46266</v>
       </c>
@@ -17688,6 +17769,9 @@
       <c r="E588">
         <v>11.62</v>
       </c>
+      <c r="F588">
+        <v>8.5</v>
+      </c>
       <c r="G588" s="2">
         <v>46266</v>
       </c>
@@ -17716,6 +17800,9 @@
       <c r="E589">
         <v>7.188</v>
       </c>
+      <c r="F589">
+        <v>16.69</v>
+      </c>
       <c r="G589" s="2">
         <v>46266</v>
       </c>
@@ -17744,6 +17831,9 @@
       <c r="E590">
         <v>42.54</v>
       </c>
+      <c r="F590">
+        <v>-0.5600000000000001</v>
+      </c>
       <c r="G590" s="2">
         <v>46266</v>
       </c>
@@ -17772,6 +17862,9 @@
       <c r="E591">
         <v>14.06</v>
       </c>
+      <c r="F591">
+        <v>-13.35</v>
+      </c>
       <c r="G591" s="2">
         <v>46266</v>
       </c>
@@ -17800,6 +17893,9 @@
       <c r="E592">
         <v>320.958</v>
       </c>
+      <c r="F592">
+        <v>5.19</v>
+      </c>
       <c r="G592" s="2">
         <v>46266</v>
       </c>
@@ -17828,6 +17924,9 @@
       <c r="E593">
         <v>6.42</v>
       </c>
+      <c r="F593">
+        <v>22.52</v>
+      </c>
       <c r="G593" s="2">
         <v>46266</v>
       </c>
@@ -17856,6 +17955,9 @@
       <c r="E594">
         <v>29.43</v>
       </c>
+      <c r="F594">
+        <v>12.11</v>
+      </c>
       <c r="G594" s="2">
         <v>46266</v>
       </c>
@@ -17884,6 +17986,9 @@
       <c r="E595">
         <v>35.59999999999999</v>
       </c>
+      <c r="F595">
+        <v>-8.369999999999999</v>
+      </c>
       <c r="G595" s="2">
         <v>46266</v>
       </c>
@@ -17912,6 +18017,9 @@
       <c r="E596">
         <v>19.8275</v>
       </c>
+      <c r="F596">
+        <v>-3.83</v>
+      </c>
       <c r="G596" s="2">
         <v>46266</v>
       </c>
@@ -17940,6 +18048,9 @@
       <c r="E597">
         <v>94.95999999999999</v>
       </c>
+      <c r="F597">
+        <v>2.77</v>
+      </c>
       <c r="G597" s="2">
         <v>46266</v>
       </c>
@@ -17968,6 +18079,9 @@
       <c r="E598">
         <v>77.61</v>
       </c>
+      <c r="F598">
+        <v>-44.26</v>
+      </c>
       <c r="G598" s="2">
         <v>46266</v>
       </c>
@@ -17996,6 +18110,9 @@
       <c r="E599">
         <v>6.222</v>
       </c>
+      <c r="F599">
+        <v>-8.19</v>
+      </c>
       <c r="G599" s="2">
         <v>46266</v>
       </c>
@@ -29591,6 +29708,12 @@
           <t>Arroz tipo 1</t>
         </is>
       </c>
+      <c r="E1016">
+        <v>12.78</v>
+      </c>
+      <c r="F1016">
+        <v>43.92</v>
+      </c>
       <c r="G1016" s="2">
         <v>46296</v>
       </c>
@@ -29616,6 +29739,12 @@
           <t>Açúcar Refinado</t>
         </is>
       </c>
+      <c r="E1017">
+        <v>13.17</v>
+      </c>
+      <c r="F1017">
+        <v>3.05</v>
+      </c>
       <c r="G1017" s="2">
         <v>46296</v>
       </c>
@@ -29641,6 +29770,12 @@
           <t>Banana</t>
         </is>
       </c>
+      <c r="E1018">
+        <v>7.188</v>
+      </c>
+      <c r="F1018">
+        <v>-42.9</v>
+      </c>
       <c r="G1018" s="2">
         <v>46296</v>
       </c>
@@ -29666,6 +29801,12 @@
           <t>Batata</t>
         </is>
       </c>
+      <c r="E1019">
+        <v>44.94</v>
+      </c>
+      <c r="F1019">
+        <v>25.04</v>
+      </c>
       <c r="G1019" s="2">
         <v>46296</v>
       </c>
@@ -29691,6 +29832,12 @@
           <t>Café em pó</t>
         </is>
       </c>
+      <c r="E1020">
+        <v>16.194</v>
+      </c>
+      <c r="F1020">
+        <v>5.88</v>
+      </c>
       <c r="G1020" s="2">
         <v>46296</v>
       </c>
@@ -29716,6 +29863,12 @@
           <t>Carne</t>
         </is>
       </c>
+      <c r="E1021">
+        <v>258.984</v>
+      </c>
+      <c r="F1021">
+        <v>10.54</v>
+      </c>
       <c r="G1021" s="2">
         <v>46296</v>
       </c>
@@ -29741,6 +29894,12 @@
           <t>Farinha de Trigo</t>
         </is>
       </c>
+      <c r="E1022">
+        <v>5.745</v>
+      </c>
+      <c r="F1022">
+        <v>-4.01</v>
+      </c>
       <c r="G1022" s="2">
         <v>46296</v>
       </c>
@@ -29766,6 +29925,12 @@
           <t>Feijão Preto</t>
         </is>
       </c>
+      <c r="E1023">
+        <v>28.4625</v>
+      </c>
+      <c r="F1023">
+        <v>49.88</v>
+      </c>
       <c r="G1023" s="2">
         <v>46296</v>
       </c>
@@ -29791,6 +29956,12 @@
           <t>Leite</t>
         </is>
       </c>
+      <c r="E1024">
+        <v>38.1375</v>
+      </c>
+      <c r="F1024">
+        <v>3.35</v>
+      </c>
       <c r="G1024" s="2">
         <v>46296</v>
       </c>
@@ -29816,6 +29987,12 @@
           <t>Manteiga</t>
         </is>
       </c>
+      <c r="E1025">
+        <v>21.7425</v>
+      </c>
+      <c r="F1025">
+        <v>1.76</v>
+      </c>
       <c r="G1025" s="2">
         <v>46296</v>
       </c>
@@ -29841,6 +30018,12 @@
           <t>Pão Francês</t>
         </is>
       </c>
+      <c r="E1026">
+        <v>92.37</v>
+      </c>
+      <c r="F1026">
+        <v>3.32</v>
+      </c>
       <c r="G1026" s="2">
         <v>46296</v>
       </c>
@@ -29866,6 +30049,12 @@
           <t>Tomate</t>
         </is>
       </c>
+      <c r="E1027">
+        <v>134.91</v>
+      </c>
+      <c r="F1027">
+        <v>57.96</v>
+      </c>
       <c r="G1027" s="2">
         <v>46296</v>
       </c>
@@ -29891,6 +30080,12 @@
           <t>Óleo de Soja</t>
         </is>
       </c>
+      <c r="E1028">
+        <v>6.920999999999999</v>
+      </c>
+      <c r="F1028">
+        <v>11.61</v>
+      </c>
       <c r="G1028" s="2">
         <v>46296</v>
       </c>
@@ -29919,6 +30114,9 @@
       <c r="E1029">
         <v>12.49</v>
       </c>
+      <c r="F1029">
+        <v>-2.27</v>
+      </c>
       <c r="G1029" s="2">
         <v>46266</v>
       </c>
@@ -29947,6 +30145,9 @@
       <c r="E1030">
         <v>11.37</v>
       </c>
+      <c r="F1030">
+        <v>-13.67</v>
+      </c>
       <c r="G1030" s="2">
         <v>46266</v>
       </c>
@@ -29975,6 +30176,9 @@
       <c r="E1031">
         <v>7.744</v>
       </c>
+      <c r="F1031">
+        <v>7.74</v>
+      </c>
       <c r="G1031" s="2">
         <v>46266</v>
       </c>
@@ -30003,6 +30207,9 @@
       <c r="E1032">
         <v>41.94</v>
       </c>
+      <c r="F1032">
+        <v>-6.68</v>
+      </c>
       <c r="G1032" s="2">
         <v>46266</v>
       </c>
@@ -30031,6 +30238,9 @@
       <c r="E1033">
         <v>15.528</v>
       </c>
+      <c r="F1033">
+        <v>-4.11</v>
+      </c>
       <c r="G1033" s="2">
         <v>46266</v>
       </c>
@@ -30059,6 +30269,9 @@
       <c r="E1034">
         <v>237.534</v>
       </c>
+      <c r="F1034">
+        <v>-8.279999999999999</v>
+      </c>
       <c r="G1034" s="2">
         <v>46266</v>
       </c>
@@ -30087,6 +30300,9 @@
       <c r="E1035">
         <v>5.859999999999999</v>
       </c>
+      <c r="F1035">
+        <v>2</v>
+      </c>
       <c r="G1035" s="2">
         <v>46266</v>
       </c>
@@ -30115,6 +30331,9 @@
       <c r="E1036">
         <v>29.22</v>
       </c>
+      <c r="F1036">
+        <v>2.66</v>
+      </c>
       <c r="G1036" s="2">
         <v>46266</v>
       </c>
@@ -30143,6 +30362,9 @@
       <c r="E1037">
         <v>38.4</v>
       </c>
+      <c r="F1037">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="G1037" s="2">
         <v>46266</v>
       </c>
@@ -30171,6 +30393,9 @@
       <c r="E1038">
         <v>21.8675</v>
       </c>
+      <c r="F1038">
+        <v>0.57</v>
+      </c>
       <c r="G1038" s="2">
         <v>46266</v>
       </c>
@@ -30199,6 +30424,9 @@
       <c r="E1039">
         <v>85.40000000000001</v>
       </c>
+      <c r="F1039">
+        <v>-7.55</v>
+      </c>
       <c r="G1039" s="2">
         <v>46266</v>
       </c>
@@ -30227,6 +30455,9 @@
       <c r="E1040">
         <v>110.79</v>
       </c>
+      <c r="F1040">
+        <v>-17.88</v>
+      </c>
       <c r="G1040" s="2">
         <v>46266</v>
       </c>
@@ -30255,6 +30486,9 @@
       <c r="E1041">
         <v>6.792000000000001</v>
       </c>
+      <c r="F1041">
+        <v>-1.86</v>
+      </c>
       <c r="G1041" s="2">
         <v>46266</v>
       </c>
@@ -37015,7 +37249,7 @@
         </is>
       </c>
       <c r="E1302">
-        <v>10.47</v>
+        <v>10.67</v>
       </c>
       <c r="G1302" s="2">
         <v>46296</v>
@@ -37043,7 +37277,7 @@
         </is>
       </c>
       <c r="E1303">
-        <v>10.575</v>
+        <v>10.84</v>
       </c>
       <c r="G1303" s="2">
         <v>46296</v>
@@ -37071,7 +37305,7 @@
         </is>
       </c>
       <c r="E1304">
-        <v>4.548</v>
+        <v>5.748</v>
       </c>
       <c r="G1304" s="2">
         <v>46296</v>
@@ -37099,7 +37333,7 @@
         </is>
       </c>
       <c r="E1305">
-        <v>31.14</v>
+        <v>36.54</v>
       </c>
       <c r="G1305" s="2">
         <v>46296</v>
@@ -37127,7 +37361,7 @@
         </is>
       </c>
       <c r="E1306">
-        <v>13.074</v>
+        <v>14.314</v>
       </c>
       <c r="G1306" s="2">
         <v>46296</v>
@@ -37155,7 +37389,7 @@
         </is>
       </c>
       <c r="E1307">
-        <v>355.575</v>
+        <v>366.6299999999999</v>
       </c>
       <c r="G1307" s="2">
         <v>46296</v>
@@ -37183,7 +37417,7 @@
         </is>
       </c>
       <c r="E1308">
-        <v>5.31</v>
+        <v>5.185</v>
       </c>
       <c r="G1308" s="2">
         <v>46296</v>
@@ -37211,7 +37445,7 @@
         </is>
       </c>
       <c r="E1309">
-        <v>25.875</v>
+        <v>25.89</v>
       </c>
       <c r="G1309" s="2">
         <v>46296</v>
@@ -37239,7 +37473,7 @@
         </is>
       </c>
       <c r="E1310">
-        <v>38.25</v>
+        <v>37.95</v>
       </c>
       <c r="G1310" s="2">
         <v>46296</v>
@@ -37267,7 +37501,7 @@
         </is>
       </c>
       <c r="E1311">
-        <v>21.4125</v>
+        <v>20.7675</v>
       </c>
       <c r="G1311" s="2">
         <v>46296</v>
@@ -37295,7 +37529,7 @@
         </is>
       </c>
       <c r="E1312">
-        <v>90.53999999999999</v>
+        <v>94.34</v>
       </c>
       <c r="G1312" s="2">
         <v>46296</v>
@@ -37323,7 +37557,7 @@
         </is>
       </c>
       <c r="E1313">
-        <v>148.86</v>
+        <v>144.21</v>
       </c>
       <c r="G1313" s="2">
         <v>46296</v>
@@ -37351,7 +37585,7 @@
         </is>
       </c>
       <c r="E1314">
-        <v>6.6645</v>
+        <v>6.69</v>
       </c>
       <c r="G1314" s="2">
         <v>46296</v>
@@ -37382,7 +37616,7 @@
         <v>10.4925</v>
       </c>
       <c r="F1315">
-        <v>0.21</v>
+        <v>-1.66</v>
       </c>
       <c r="G1315" s="2">
         <v>46266</v>
@@ -37413,7 +37647,7 @@
         <v>10.275</v>
       </c>
       <c r="F1316">
-        <v>-2.84</v>
+        <v>-5.21</v>
       </c>
       <c r="G1316" s="2">
         <v>46266</v>
@@ -37444,7 +37678,7 @@
         <v>6.435</v>
       </c>
       <c r="F1317">
-        <v>41.49</v>
+        <v>11.95</v>
       </c>
       <c r="G1317" s="2">
         <v>46266</v>
@@ -37475,7 +37709,7 @@
         <v>35.77500000000001</v>
       </c>
       <c r="F1318">
-        <v>14.88</v>
+        <v>-2.09</v>
       </c>
       <c r="G1318" s="2">
         <v>46266</v>
@@ -37506,7 +37740,7 @@
         <v>13.294</v>
       </c>
       <c r="F1319">
-        <v>1.68</v>
+        <v>-7.13</v>
       </c>
       <c r="G1319" s="2">
         <v>46266</v>
@@ -37537,7 +37771,7 @@
         <v>327.7449999999999</v>
       </c>
       <c r="F1320">
-        <v>-7.83</v>
+        <v>-10.61</v>
       </c>
       <c r="G1320" s="2">
         <v>46266</v>
@@ -37568,7 +37802,7 @@
         <v>5.535</v>
       </c>
       <c r="F1321">
-        <v>4.24</v>
+        <v>6.75</v>
       </c>
       <c r="G1321" s="2">
         <v>46266</v>
@@ -37599,7 +37833,7 @@
         <v>26.80875</v>
       </c>
       <c r="F1322">
-        <v>3.61</v>
+        <v>3.55</v>
       </c>
       <c r="G1322" s="2">
         <v>46266</v>
@@ -37630,7 +37864,7 @@
         <v>37.9875</v>
       </c>
       <c r="F1323">
-        <v>-0.6899999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="G1323" s="2">
         <v>46266</v>
@@ -37661,7 +37895,7 @@
         <v>20.30125</v>
       </c>
       <c r="F1324">
-        <v>-5.19</v>
+        <v>-2.25</v>
       </c>
       <c r="G1324" s="2">
         <v>46266</v>
@@ -37692,7 +37926,7 @@
         <v>93.64999999999999</v>
       </c>
       <c r="F1325">
-        <v>3.43</v>
+        <v>-0.73</v>
       </c>
       <c r="G1325" s="2">
         <v>46266</v>
@@ -37723,7 +37957,7 @@
         <v>102.765</v>
       </c>
       <c r="F1326">
-        <v>-30.97</v>
+        <v>-28.74</v>
       </c>
       <c r="G1326" s="2">
         <v>46266</v>
@@ -37754,7 +37988,7 @@
         <v>6.303000000000001</v>
       </c>
       <c r="F1327">
-        <v>-5.42</v>
+        <v>-5.78</v>
       </c>
       <c r="G1327" s="2">
         <v>46266</v>
@@ -50950,6 +51184,9 @@
           <t>Arroz tipo 1</t>
         </is>
       </c>
+      <c r="E1822">
+        <v>12.6</v>
+      </c>
       <c r="G1822" s="2">
         <v>46296</v>
       </c>
@@ -50975,6 +51212,9 @@
           <t>Açúcar Refinado</t>
         </is>
       </c>
+      <c r="E1823">
+        <v>12.13</v>
+      </c>
       <c r="G1823" s="2">
         <v>46296</v>
       </c>
@@ -51000,6 +51240,9 @@
           <t>Banana</t>
         </is>
       </c>
+      <c r="E1824">
+        <v>5.58</v>
+      </c>
       <c r="G1824" s="2">
         <v>46296</v>
       </c>
@@ -51025,6 +51268,9 @@
           <t>Batata</t>
         </is>
       </c>
+      <c r="E1825">
+        <v>38.14</v>
+      </c>
       <c r="G1825" s="2">
         <v>46296</v>
       </c>
@@ -51050,6 +51296,9 @@
           <t>Café em pó</t>
         </is>
       </c>
+      <c r="E1826">
+        <v>14.936</v>
+      </c>
       <c r="G1826" s="2">
         <v>46296</v>
       </c>
@@ -51075,6 +51324,9 @@
           <t>Carne</t>
         </is>
       </c>
+      <c r="E1827">
+        <v>343.09</v>
+      </c>
       <c r="G1827" s="2">
         <v>46296</v>
       </c>
@@ -51100,6 +51352,9 @@
           <t>Farinha de Trigo</t>
         </is>
       </c>
+      <c r="E1828">
+        <v>6.98</v>
+      </c>
       <c r="G1828" s="2">
         <v>46296</v>
       </c>
@@ -51125,6 +51380,9 @@
           <t>Feijão Preto</t>
         </is>
       </c>
+      <c r="E1829">
+        <v>30.66</v>
+      </c>
       <c r="G1829" s="2">
         <v>46296</v>
       </c>
@@ -51150,6 +51408,9 @@
           <t>Leite</t>
         </is>
       </c>
+      <c r="E1830">
+        <v>38.2875</v>
+      </c>
       <c r="G1830" s="2">
         <v>46296</v>
       </c>
@@ -51175,6 +51436,9 @@
           <t>Manteiga</t>
         </is>
       </c>
+      <c r="E1831">
+        <v>17.65</v>
+      </c>
       <c r="G1831" s="2">
         <v>46296</v>
       </c>
@@ -51200,6 +51464,9 @@
           <t>Pão Francês</t>
         </is>
       </c>
+      <c r="E1832">
+        <v>73.52000000000001</v>
+      </c>
       <c r="G1832" s="2">
         <v>46296</v>
       </c>
@@ -51225,6 +51492,9 @@
           <t>Tomate</t>
         </is>
       </c>
+      <c r="E1833">
+        <v>123.72</v>
+      </c>
       <c r="G1833" s="2">
         <v>46296</v>
       </c>
@@ -51250,6 +51520,9 @@
           <t>Óleo de Soja</t>
         </is>
       </c>
+      <c r="E1834">
+        <v>6.501</v>
+      </c>
       <c r="G1834" s="2">
         <v>46296</v>
       </c>
@@ -51278,6 +51551,9 @@
       <c r="E1835">
         <v>12.34</v>
       </c>
+      <c r="F1835">
+        <v>-2.06</v>
+      </c>
       <c r="G1835" s="2">
         <v>46266</v>
       </c>
@@ -51306,6 +51582,9 @@
       <c r="E1836">
         <v>11.1</v>
       </c>
+      <c r="F1836">
+        <v>-8.49</v>
+      </c>
       <c r="G1836" s="2">
         <v>46266</v>
       </c>
@@ -51334,6 +51613,9 @@
       <c r="E1837">
         <v>5.303999999999999</v>
       </c>
+      <c r="F1837">
+        <v>-4.95</v>
+      </c>
       <c r="G1837" s="2">
         <v>46266</v>
       </c>
@@ -51362,6 +51644,9 @@
       <c r="E1838">
         <v>41.94</v>
       </c>
+      <c r="F1838">
+        <v>9.960000000000001</v>
+      </c>
       <c r="G1838" s="2">
         <v>46266</v>
       </c>
@@ -51390,6 +51675,9 @@
       <c r="E1839">
         <v>15.294</v>
       </c>
+      <c r="F1839">
+        <v>2.4</v>
+      </c>
       <c r="G1839" s="2">
         <v>46266</v>
       </c>
@@ -51418,6 +51706,9 @@
       <c r="E1840">
         <v>336.6</v>
       </c>
+      <c r="F1840">
+        <v>-1.89</v>
+      </c>
       <c r="G1840" s="2">
         <v>46266</v>
       </c>
@@ -51446,6 +51737,9 @@
       <c r="E1841">
         <v>6.645</v>
       </c>
+      <c r="F1841">
+        <v>-4.8</v>
+      </c>
       <c r="G1841" s="2">
         <v>46266</v>
       </c>
@@ -51474,6 +51768,9 @@
       <c r="E1842">
         <v>32.58</v>
       </c>
+      <c r="F1842">
+        <v>6.26</v>
+      </c>
       <c r="G1842" s="2">
         <v>46266</v>
       </c>
@@ -51502,6 +51799,9 @@
       <c r="E1843">
         <v>42.59999999999999</v>
       </c>
+      <c r="F1843">
+        <v>11.26</v>
+      </c>
       <c r="G1843" s="2">
         <v>46266</v>
       </c>
@@ -51530,6 +51830,9 @@
       <c r="E1844">
         <v>20.7275</v>
       </c>
+      <c r="F1844">
+        <v>17.44</v>
+      </c>
       <c r="G1844" s="2">
         <v>46266</v>
       </c>
@@ -51558,6 +51861,9 @@
       <c r="E1845">
         <v>74.61</v>
       </c>
+      <c r="F1845">
+        <v>1.48</v>
+      </c>
       <c r="G1845" s="2">
         <v>46266</v>
       </c>
@@ -51586,6 +51892,9 @@
       <c r="E1846">
         <v>87.99000000000001</v>
       </c>
+      <c r="F1846">
+        <v>-28.88</v>
+      </c>
       <c r="G1846" s="2">
         <v>46266</v>
       </c>
@@ -51613,6 +51922,9 @@
       </c>
       <c r="E1847">
         <v>6.906</v>
+      </c>
+      <c r="F1847">
+        <v>6.23</v>
       </c>
       <c r="G1847" s="2">
         <v>46266</v>
